--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -346,7 +346,7 @@
     <t>p6</t>
   </si>
   <si>
-    <t>4 stiffeners: one placed, three rotated</t>
+    <t>ROT round the column, then COPY twice -&gt; 24</t>
   </si>
   <si>
     <t>ASSY</t>
@@ -364,16 +364,16 @@
     <t>Z</t>
   </si>
   <si>
-    <t>ADD / MIR / COPY, and an ASSY as a source</t>
+    <t>COPY</t>
+  </si>
+  <si>
+    <t>ADD / MIR / COPY. 22 members, copied to 3 bents</t>
   </si>
   <si>
     <t>as.bent</t>
   </si>
   <si>
     <t>MIR</t>
-  </si>
-  <si>
-    <t>COPY</t>
   </si>
   <si>
     <t>END</t>
@@ -2496,76 +2496,82 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" t="s">
+        <v>117</v>
+      </c>
+      <c r="F67">
+        <v>2400</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C68" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>3000</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D68" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" t="s">
-        <v>114</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" t="s">
-        <v>114</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D70" t="s">
         <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F70">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -2573,11 +2579,8 @@
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -2585,22 +2588,25 @@
         <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F71">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -2611,7 +2617,7 @@
         <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" t="s">
         <v>99</v>
@@ -2637,7 +2643,7 @@
         <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D73" t="s">
         <v>102</v>
@@ -2663,7 +2669,7 @@
         <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D74" t="s">
         <v>100</v>
@@ -2689,13 +2695,13 @@
         <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E75" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F75">
         <v>0</v>

--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -1310,7 +1310,7 @@
         <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H21">
         <v>150</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>-60</v>
+        <v>-130</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2283,16 +2283,16 @@
         <v>2400</v>
       </c>
       <c r="J59">
-        <v>-60</v>
+        <v>-130</v>
       </c>
       <c r="K59">
         <v>3000</v>
       </c>
       <c r="L59">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="M59">
-        <v>90</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>2400</v>
       </c>
       <c r="G60">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2324,16 +2324,16 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="K60">
         <v>3000</v>
       </c>
       <c r="L60">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="M60">
-        <v>90</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">

--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="123">
   <si>
     <t>BASIC example - every keyword, one small model</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>MIR</t>
+  </si>
+  <si>
+    <t>BASE sits on brc_1, whose line starts at y -150</t>
   </si>
   <si>
     <t>END</t>
@@ -2274,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>-130</v>
+        <v>-150</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2283,7 +2286,7 @@
         <v>2400</v>
       </c>
       <c r="J59">
-        <v>-130</v>
+        <v>-150</v>
       </c>
       <c r="K59">
         <v>3000</v>
@@ -2315,7 +2318,7 @@
         <v>2400</v>
       </c>
       <c r="G60">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2324,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="K60">
         <v>3000</v>
@@ -2637,7 +2640,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>112</v>
@@ -2655,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="H73">
         <v>25</v>
@@ -2721,7 +2724,7 @@
         <v>11</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="122">
   <si>
     <t>BASIC example - every keyword, one small model</t>
   </si>
@@ -326,9 +326,6 @@
   </si>
   <si>
     <t>sc.brc_2</t>
-  </si>
-  <si>
-    <t>sc.str_1</t>
   </si>
   <si>
     <t># ASSY</t>
@@ -782,7 +779,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -846,7 +843,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -875,7 +872,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -910,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -939,7 +936,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -968,7 +965,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -994,7 +991,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1017,7 +1014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1037,7 +1034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1060,7 +1057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,7 +1077,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1100,7 +1097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1252,7 +1249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -1293,7 +1290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -1334,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,7 +1360,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1392,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -1421,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
@@ -1441,7 +1438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -1470,7 +1467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
@@ -1499,7 +1496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1519,7 +1516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>11</v>
       </c>
@@ -1548,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -1577,7 +1574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
@@ -1597,7 +1594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1626,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1655,7 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -2350,7 +2347,7 @@
         <v>102</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E61" t="s">
         <v>11</v>
@@ -2403,21 +2400,21 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
       </c>
       <c r="D64" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" t="s">
         <v>107</v>
-      </c>
-      <c r="E64" t="s">
-        <v>108</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2432,27 +2429,27 @@
         <v>10</v>
       </c>
       <c r="J64" t="s">
+        <v>108</v>
+      </c>
+      <c r="K64" t="s">
         <v>109</v>
       </c>
-      <c r="K64" t="s">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" t="s">
         <v>112</v>
-      </c>
-      <c r="C65" t="s">
-        <v>113</v>
       </c>
       <c r="D65" t="s">
         <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F65">
         <v>100</v>
@@ -2464,21 +2461,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" t="s">
         <v>112</v>
       </c>
-      <c r="C66" t="s">
-        <v>113</v>
-      </c>
       <c r="D66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2490,7 +2487,7 @@
         <v>25</v>
       </c>
       <c r="I66" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J66">
         <v>90</v>
@@ -2499,21 +2496,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" t="s">
         <v>112</v>
       </c>
-      <c r="C67" t="s">
-        <v>113</v>
-      </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F67">
         <v>2400</v>
@@ -2528,21 +2525,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68" t="s">
         <v>112</v>
       </c>
-      <c r="C68" t="s">
-        <v>113</v>
-      </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2557,21 +2554,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C70" t="s">
         <v>118</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" t="s">
-        <v>119</v>
       </c>
       <c r="D70" t="s">
         <v>78</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2583,21 +2580,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D71" t="s">
         <v>78</v>
       </c>
       <c r="E71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F71">
         <v>1200</v>
@@ -2612,21 +2609,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D72" t="s">
         <v>99</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2638,21 +2635,21 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C73" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D73" t="s">
         <v>102</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2664,21 +2661,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D74" t="s">
         <v>100</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F74">
         <v>1200</v>
@@ -2690,21 +2687,21 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2719,16 +2716,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="130">
   <si>
     <t>BASIC example - every keyword, one small model</t>
   </si>
@@ -374,6 +374,30 @@
   </si>
   <si>
     <t>BASE sits on brc_1, whose line starts at y -150</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>BASIC - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -770,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -779,7 +803,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -814,7 +838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -843,7 +867,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -872,7 +896,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -907,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -936,7 +960,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -965,7 +989,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -991,7 +1015,8 @@
         <v>320</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1014,7 +1039,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1034,7 +1059,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1057,7 +1082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1077,7 +1102,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1097,7 +1123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1117,6 +1143,7 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>11</v>
@@ -1249,7 +1276,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -1290,7 +1317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -1331,7 +1358,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,7 +1388,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -1418,7 +1446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
@@ -1438,7 +1466,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,7 +1495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
@@ -1496,7 +1524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,7 +1544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>11</v>
       </c>
@@ -1545,7 +1573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -1574,7 +1602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,7 +1622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1623,7 +1651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1652,7 +1680,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -2034,6 +2063,7 @@
         <v>79</v>
       </c>
     </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>11</v>
@@ -2083,6 +2113,7 @@
         <v>21</v>
       </c>
     </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>11</v>
@@ -2132,6 +2163,7 @@
         <v>53</v>
       </c>
     </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>11</v>
@@ -2210,6 +2242,7 @@
         <v>79</v>
       </c>
     </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>11</v>
@@ -2400,7 +2433,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
@@ -2435,7 +2469,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>110</v>
       </c>
@@ -2461,7 +2495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
@@ -2496,7 +2530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
@@ -2525,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
@@ -2554,7 +2588,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>117</v>
       </c>
@@ -2580,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -2609,7 +2644,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -2635,7 +2670,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>120</v>
       </c>
@@ -2661,7 +2696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -2687,7 +2722,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -2716,12 +2751,63 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" s="3" t="s">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>121</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76">
+        <v>50</v>
+      </c>
+      <c r="H76" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>124</v>
+      </c>
+      <c r="C77" t="s">
+        <v>125</v>
+      </c>
+      <c r="D77" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78">
+        <v>20</v>
+      </c>
+      <c r="F78" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="122">
   <si>
     <t>BASIC example - every keyword, one small model</t>
   </si>
@@ -374,30 +374,6 @@
   </si>
   <si>
     <t>BASE sits on brc_1, whose line starts at y -150</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>BASIC - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -794,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -803,7 +779,7 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -838,7 +814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -867,7 +843,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -896,7 +872,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -931,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -960,7 +936,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -989,7 +965,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1015,8 +991,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -1039,7 +1014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1059,7 +1034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1082,7 +1057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1077,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1123,7 +1097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -1143,7 +1117,6 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>11</v>
@@ -1276,7 +1249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -1317,7 +1290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -1358,8 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,7 +1360,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1417,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -1446,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>67</v>
       </c>
@@ -1466,7 +1438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,7 +1467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
@@ -1524,7 +1496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1544,7 +1516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>11</v>
       </c>
@@ -1573,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>11</v>
       </c>
@@ -1602,7 +1574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
@@ -1622,7 +1594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1651,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1680,8 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -2063,7 +2034,6 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>11</v>
@@ -2113,7 +2083,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>11</v>
@@ -2163,7 +2132,6 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>11</v>
@@ -2242,7 +2210,6 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>11</v>
@@ -2433,8 +2400,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
@@ -2469,7 +2435,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>110</v>
       </c>
@@ -2495,7 +2461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
@@ -2530,7 +2496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
@@ -2559,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
@@ -2588,8 +2554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>117</v>
       </c>
@@ -2615,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -2644,7 +2609,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -2670,7 +2635,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>120</v>
       </c>
@@ -2696,7 +2661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -2722,7 +2687,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -2751,63 +2716,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>122</v>
-      </c>
-      <c r="G76">
-        <v>50</v>
-      </c>
-      <c r="H76" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>124</v>
-      </c>
-      <c r="C77" t="s">
-        <v>125</v>
-      </c>
-      <c r="D77" t="s">
-        <v>126</v>
-      </c>
-      <c r="E77">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>124</v>
-      </c>
-      <c r="C78" t="s">
-        <v>48</v>
-      </c>
-      <c r="D78" t="s">
-        <v>126</v>
-      </c>
-      <c r="E78">
-        <v>20</v>
-      </c>
-      <c r="F78" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
